--- a/customer_satisfaction_evaluation_forms/040_store_layout_satisfaction_poll--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/040_store_layout_satisfaction_poll--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'too_small'}</t>
+          <t>too_small</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'too small'}</t>
+          <t>too small</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'too_big'}</t>
+          <t>too_big</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'too big'}</t>
+          <t>too big</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'too_cluttered'}</t>
+          <t>too_cluttered</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'too cluttered'}</t>
+          <t>too cluttered</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'too_slow'}</t>
+          <t>too_slow</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'too slow'}</t>
+          <t>too slow</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'too_fast'}</t>
+          <t>too_fast</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'too fast'}</t>
+          <t>too fast</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'too_hard_to_navigate'}</t>
+          <t>too_hard_to_navigate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'too hard to navigate'}</t>
+          <t>too hard to navigate</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'too_easy_to_navigate'}</t>
+          <t>too_easy_to_navigate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'too easy to navigate'}</t>
+          <t>too easy to navigate</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'less_clutter'}</t>
+          <t>less_clutter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'less clutter'}</t>
+          <t>less clutter</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'more_organized'}</t>
+          <t>more_organized</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'more organized'}</t>
+          <t>more organized</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'more_space'}</t>
+          <t>more_space</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'more space'}</t>
+          <t>more space</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'more_appealing'}</t>
+          <t>more_appealing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'more appealing'}</t>
+          <t>more appealing</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'more_products'}</t>
+          <t>more_products</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'more products'}</t>
+          <t>more products</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'more_promotions'}</t>
+          <t>more_promotions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'more promotions'}</t>
+          <t>more promotions</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'more_events'}</t>
+          <t>more_events</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'more events'}</t>
+          <t>more events</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'more_sales_associate_help'}</t>
+          <t>more_sales_associate_help</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'more sales associate help'}</t>
+          <t>more sales associate help</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'more_appealing'}</t>
+          <t>more_appealing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'more appealing'}</t>
+          <t>more appealing</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'more_organized'}</t>
+          <t>more_organized</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'more organized'}</t>
+          <t>more organized</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'more_space'}</t>
+          <t>more_space</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'more space'}</t>
+          <t>more space</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'better_product_variety'}</t>
+          <t>better_product_variety</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'better product variety'}</t>
+          <t>better product variety</t>
         </is>
       </c>
     </row>
